--- a/data/stats/supp_tables/spweedcountsPERENN-till-pairs.xlsx
+++ b/data/stats/supp_tables/spweedcountsPERENN-till-pairs.xlsx
@@ -423,19 +423,19 @@
         </is>
       </c>
       <c r="E2">
-        <v>-2.586255343448981</v>
+        <v>-2.586255343448816</v>
       </c>
       <c r="F2">
-        <v>0.3828672795077999</v>
+        <v>0.3828672319049167</v>
       </c>
       <c r="G2">
-        <v>354</v>
+        <v>171.428571428585</v>
       </c>
       <c r="H2">
-        <v>-6.754965707108154</v>
+        <v>-6.754966546970259</v>
       </c>
       <c r="I2">
-        <v>1.734185017809864E-10</v>
+        <v>6.394090812378295E-10</v>
       </c>
     </row>
     <row r="3">
@@ -460,19 +460,19 @@
         </is>
       </c>
       <c r="E3">
-        <v>-2.509687546030887</v>
+        <v>-2.509687546030736</v>
       </c>
       <c r="F3">
-        <v>0.3828672795078</v>
+        <v>0.3828672319049167</v>
       </c>
       <c r="G3">
-        <v>354</v>
+        <v>171.428571428583</v>
       </c>
       <c r="H3">
-        <v>-6.554980486337846</v>
+        <v>-6.554981301335301</v>
       </c>
       <c r="I3">
-        <v>5.876031883289556E-10</v>
+        <v>1.88306470416677E-09</v>
       </c>
     </row>
     <row r="4">
@@ -497,19 +497,19 @@
         </is>
       </c>
       <c r="E4">
-        <v>0.07656779741809396</v>
+        <v>0.07656779741808066</v>
       </c>
       <c r="F4">
-        <v>0.3828672795078187</v>
+        <v>0.382867231904893</v>
       </c>
       <c r="G4">
-        <v>354</v>
+        <v>171.4285714285788</v>
       </c>
       <c r="H4">
-        <v>0.1999852207702965</v>
+        <v>0.199985245634969</v>
       </c>
       <c r="I4">
-        <v>0.9781946006941252</v>
+        <v>0.9781960362502924</v>
       </c>
     </row>
     <row r="5">
@@ -534,19 +534,19 @@
         </is>
       </c>
       <c r="E5">
-        <v>-1.556157904839167</v>
+        <v>-1.556157904839185</v>
       </c>
       <c r="F5">
-        <v>0.382867279507822</v>
+        <v>0.3828672319048944</v>
       </c>
       <c r="G5">
-        <v>354</v>
+        <v>171.4285714285622</v>
       </c>
       <c r="H5">
-        <v>-4.064483929887183</v>
+        <v>-4.064484435235606</v>
       </c>
       <c r="I5">
-        <v>0.0001750829948098387</v>
+        <v>0.0002153100660282625</v>
       </c>
     </row>
     <row r="6">
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="E6">
-        <v>-0.7583565704815599</v>
+        <v>-0.7583565704815788</v>
       </c>
       <c r="F6">
-        <v>0.3828672795078221</v>
+        <v>0.382867231904895</v>
       </c>
       <c r="G6">
-        <v>354</v>
+        <v>171.4285714285622</v>
       </c>
       <c r="H6">
-        <v>-1.980729644634118</v>
+        <v>-1.980729890903685</v>
       </c>
       <c r="I6">
-        <v>0.1184592952411807</v>
+        <v>0.1200586020296195</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="E7">
-        <v>0.7978013343576071</v>
+        <v>0.7978013343576059</v>
       </c>
       <c r="F7">
-        <v>0.3828672795078215</v>
+        <v>0.3828672319048946</v>
       </c>
       <c r="G7">
-        <v>354</v>
+        <v>171.4285714285684</v>
       </c>
       <c r="H7">
-        <v>2.083754285253068</v>
+        <v>2.083754544331916</v>
       </c>
       <c r="I7">
-        <v>0.09465443379976146</v>
+        <v>0.09621327833274806</v>
       </c>
     </row>
     <row r="8">
@@ -645,19 +645,19 @@
         </is>
       </c>
       <c r="E8">
-        <v>-0.3994691759309185</v>
+        <v>-0.3994691759309296</v>
       </c>
       <c r="F8">
-        <v>0.3828672795078218</v>
+        <v>0.3828672319048939</v>
       </c>
       <c r="G8">
-        <v>354</v>
+        <v>171.4285714285664</v>
       </c>
       <c r="H8">
-        <v>-1.043362014232291</v>
+        <v>-1.043362143956367</v>
       </c>
       <c r="I8">
-        <v>0.5500184690699681</v>
+        <v>0.5506096668511944</v>
       </c>
     </row>
     <row r="9">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="E9">
-        <v>0.1059122325484005</v>
+        <v>0.1059122325483898</v>
       </c>
       <c r="F9">
-        <v>0.3828672795078216</v>
+        <v>0.3828672319048945</v>
       </c>
       <c r="G9">
-        <v>354</v>
+        <v>171.4285714285622</v>
       </c>
       <c r="H9">
-        <v>0.2766291041756072</v>
+        <v>0.2766291385696303</v>
       </c>
       <c r="I9">
-        <v>0.9586992831283598</v>
+        <v>0.9587044403017153</v>
       </c>
     </row>
     <row r="10">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="E10">
-        <v>0.505381408479319</v>
+        <v>0.5053814084793194</v>
       </c>
       <c r="F10">
-        <v>0.3828672795078207</v>
+        <v>0.3828672319048944</v>
       </c>
       <c r="G10">
-        <v>354</v>
+        <v>171.4285714285684</v>
       </c>
       <c r="H10">
-        <v>1.319991118407902</v>
+        <v>1.319991282525996</v>
       </c>
       <c r="I10">
-        <v>0.3849724379406569</v>
+        <v>0.3860234060423363</v>
       </c>
     </row>
     <row r="11">
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="E11">
-        <v>-0.5782965492048371</v>
+        <v>-0.5782965492048534</v>
       </c>
       <c r="F11">
-        <v>0.3828672795078225</v>
+        <v>0.3828672319048944</v>
       </c>
       <c r="G11">
-        <v>354</v>
+        <v>171.4285714285622</v>
       </c>
       <c r="H11">
-        <v>-1.510436070557504</v>
+        <v>-1.510436258354187</v>
       </c>
       <c r="I11">
-        <v>0.2872152386417043</v>
+        <v>0.2885505449395239</v>
       </c>
     </row>
     <row r="12">
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="E12">
-        <v>-0.3994691759309179</v>
+        <v>-0.3994691759309346</v>
       </c>
       <c r="F12">
-        <v>0.3828672795078223</v>
+        <v>0.3828672319048951</v>
       </c>
       <c r="G12">
-        <v>354</v>
+        <v>171.4285714285622</v>
       </c>
       <c r="H12">
-        <v>-1.043362014232288</v>
+        <v>-1.043362143956376</v>
       </c>
       <c r="I12">
-        <v>0.5500184690699699</v>
+        <v>0.5506096668511884</v>
       </c>
     </row>
     <row r="13">
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E13">
-        <v>0.1788273732739191</v>
+        <v>0.1788273732739188</v>
       </c>
       <c r="F13">
-        <v>0.3828672795078213</v>
+        <v>0.3828672319048949</v>
       </c>
       <c r="G13">
-        <v>354</v>
+        <v>171.4285714285684</v>
       </c>
       <c r="H13">
-        <v>0.467074056325218</v>
+        <v>0.4670741143978077</v>
       </c>
       <c r="I13">
-        <v>0.8867603445432859</v>
+        <v>0.8867990807644619</v>
       </c>
     </row>
     <row r="14">
@@ -867,19 +867,19 @@
         </is>
       </c>
       <c r="E14">
-        <v>-0.8129705490396657</v>
+        <v>-0.812970549039677</v>
       </c>
       <c r="F14">
-        <v>0.3828672795078221</v>
+        <v>0.3828672319048939</v>
       </c>
       <c r="G14">
-        <v>354</v>
+        <v>171.4285714285643</v>
       </c>
       <c r="H14">
-        <v>-2.123374319384888</v>
+        <v>-2.123374583389845</v>
       </c>
       <c r="I14">
-        <v>0.08658284718458376</v>
+        <v>0.08811791808104275</v>
       </c>
     </row>
     <row r="15">
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="E15">
-        <v>2.012279232133096E-16</v>
+        <v>-1.189326415129699E-14</v>
       </c>
       <c r="F15">
-        <v>0.3828672795078221</v>
+        <v>0.3828672319048945</v>
       </c>
       <c r="G15">
-        <v>354</v>
+        <v>171.4285714285643</v>
       </c>
       <c r="H15">
-        <v>5.255814063609436E-16</v>
+        <v>-3.106367732784016E-14</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -941,19 +941,19 @@
         </is>
       </c>
       <c r="E16">
-        <v>0.8129705490396659</v>
+        <v>0.8129705490396651</v>
       </c>
       <c r="F16">
-        <v>0.3828672795078214</v>
+        <v>0.3828672319048941</v>
       </c>
       <c r="G16">
-        <v>354</v>
+        <v>171.4285714285684</v>
       </c>
       <c r="H16">
-        <v>2.123374319384893</v>
+        <v>2.123374583389812</v>
       </c>
       <c r="I16">
-        <v>0.08658284718458265</v>
+        <v>0.08811791808104918</v>
       </c>
     </row>
     <row r="17">
@@ -978,19 +978,19 @@
         </is>
       </c>
       <c r="E17">
-        <v>-2.058409518294706</v>
+        <v>-2.058409518294616</v>
       </c>
       <c r="F17">
-        <v>0.3828672795078258</v>
+        <v>0.3828672319049093</v>
       </c>
       <c r="G17">
-        <v>354</v>
+        <v>171.4285714286058</v>
       </c>
       <c r="H17">
-        <v>-5.376300426980288</v>
+        <v>-5.376301095430001</v>
       </c>
       <c r="I17">
-        <v>4.140254693529855E-07</v>
+        <v>7.349156593283723E-07</v>
       </c>
     </row>
     <row r="18">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="E18">
-        <v>-0.7871557158715934</v>
+        <v>-0.7871557158715007</v>
       </c>
       <c r="F18">
-        <v>0.382867279507825</v>
+        <v>0.3828672319049105</v>
       </c>
       <c r="G18">
-        <v>354</v>
+        <v>171.428571428612</v>
       </c>
       <c r="H18">
-        <v>-2.055949301500719</v>
+        <v>-2.055949557122193</v>
       </c>
       <c r="I18">
-        <v>0.1006689835289321</v>
+        <v>0.1022418900195829</v>
       </c>
     </row>
     <row r="19">
@@ -1052,19 +1052,19 @@
         </is>
       </c>
       <c r="E19">
-        <v>1.271253802423112</v>
+        <v>1.271253802423115</v>
       </c>
       <c r="F19">
-        <v>0.3828672795078239</v>
+        <v>0.3828672319048957</v>
       </c>
       <c r="G19">
-        <v>354</v>
+        <v>171.428571428585</v>
       </c>
       <c r="H19">
-        <v>3.320351125479591</v>
+        <v>3.32035153830792</v>
       </c>
       <c r="I19">
-        <v>0.002847000082805362</v>
+        <v>0.00313777651778302</v>
       </c>
     </row>
     <row r="20">
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="E20">
-        <v>-1.029453214995539</v>
+        <v>-1.029453214995552</v>
       </c>
       <c r="F20">
-        <v>0.3828672795078221</v>
+        <v>0.3828672319048943</v>
       </c>
       <c r="G20">
-        <v>354</v>
+        <v>171.4285714285705</v>
       </c>
       <c r="H20">
-        <v>-2.688799148151043</v>
+        <v>-2.688799482456811</v>
       </c>
       <c r="I20">
-        <v>0.02047641503861508</v>
+        <v>0.02139026917399267</v>
       </c>
     </row>
     <row r="21">
@@ -1126,19 +1126,19 @@
         </is>
       </c>
       <c r="E21">
-        <v>-0.2118244650968007</v>
+        <v>-0.2118244650968119</v>
       </c>
       <c r="F21">
-        <v>0.3828672795078211</v>
+        <v>0.3828672319048951</v>
       </c>
       <c r="G21">
-        <v>354</v>
+        <v>171.4285714285664</v>
       </c>
       <c r="H21">
-        <v>-0.5532582083512143</v>
+        <v>-0.5532582771393438</v>
       </c>
       <c r="I21">
-        <v>0.8448727381532128</v>
+        <v>0.8449453138840468</v>
       </c>
     </row>
     <row r="22">
@@ -1163,19 +1163,19 @@
         </is>
       </c>
       <c r="E22">
-        <v>0.8176287498987387</v>
+        <v>0.8176287498987396</v>
       </c>
       <c r="F22">
-        <v>0.3828672795078211</v>
+        <v>0.3828672319048951</v>
       </c>
       <c r="G22">
-        <v>354</v>
+        <v>171.4285714285726</v>
       </c>
       <c r="H22">
-        <v>2.135540939799836</v>
+        <v>2.135541205317461</v>
       </c>
       <c r="I22">
-        <v>0.08421842882672859</v>
+        <v>0.08574535809414852</v>
       </c>
     </row>
     <row r="23">
@@ -1200,19 +1200,19 @@
         </is>
       </c>
       <c r="E23">
-        <v>-0.6612436396096898</v>
+        <v>-0.6612436396096952</v>
       </c>
       <c r="F23">
-        <v>0.3828672795078207</v>
+        <v>0.382867231904894</v>
       </c>
       <c r="G23">
-        <v>354</v>
+        <v>171.4285714285767</v>
       </c>
       <c r="H23">
-        <v>-1.727083182610236</v>
+        <v>-1.72708339734321</v>
       </c>
       <c r="I23">
-        <v>0.1965040176818266</v>
+        <v>0.1980529611091838</v>
       </c>
     </row>
     <row r="24">
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="E24">
-        <v>-0.25461024090763</v>
+        <v>-0.2546102409076358</v>
       </c>
       <c r="F24">
-        <v>0.3828672795078222</v>
+        <v>0.3828672319048948</v>
       </c>
       <c r="G24">
-        <v>354</v>
+        <v>171.4285714285726</v>
       </c>
       <c r="H24">
-        <v>-0.6650091416402381</v>
+        <v>-0.6650092243226542</v>
       </c>
       <c r="I24">
-        <v>0.7839397694818315</v>
+        <v>0.7840800772826522</v>
       </c>
     </row>
     <row r="25">
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="E25">
-        <v>0.4066333987020598</v>
+        <v>0.4066333987020594</v>
       </c>
       <c r="F25">
-        <v>0.3828672795078217</v>
+        <v>0.3828672319048939</v>
       </c>
       <c r="G25">
-        <v>354</v>
+        <v>171.4285714285684</v>
       </c>
       <c r="H25">
-        <v>1.062074040969992</v>
+        <v>1.062074173020555</v>
       </c>
       <c r="I25">
-        <v>0.5382940872297154</v>
+        <v>0.5389149887355981</v>
       </c>
     </row>
     <row r="26">
@@ -1311,19 +1311,19 @@
         </is>
       </c>
       <c r="E26">
-        <v>-0.8285670756064956</v>
+        <v>-0.8285670756065062</v>
       </c>
       <c r="F26">
-        <v>0.3828672795078221</v>
+        <v>0.3828672319048943</v>
       </c>
       <c r="G26">
-        <v>354</v>
+        <v>171.4285714285726</v>
       </c>
       <c r="H26">
-        <v>-2.164110437098785</v>
+        <v>-2.164110706168569</v>
       </c>
       <c r="I26">
-        <v>0.07887089129585445</v>
+        <v>0.08037722763241961</v>
       </c>
     </row>
     <row r="27">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="E27">
-        <v>-0.521798408736954</v>
+        <v>-0.5217984087369646</v>
       </c>
       <c r="F27">
-        <v>0.3828672795078227</v>
+        <v>0.382867231904895</v>
       </c>
       <c r="G27">
-        <v>354</v>
+        <v>171.4285714285726</v>
       </c>
       <c r="H27">
-        <v>-1.362870207680656</v>
+        <v>-1.362870377130055</v>
       </c>
       <c r="I27">
-        <v>0.3616084699843866</v>
+        <v>0.3627286757686554</v>
       </c>
     </row>
     <row r="28">
@@ -1385,19 +1385,19 @@
         </is>
       </c>
       <c r="E28">
-        <v>0.3067686668695415</v>
+        <v>0.3067686668695416</v>
       </c>
       <c r="F28">
-        <v>0.3828672795078213</v>
+        <v>0.3828672319048955</v>
       </c>
       <c r="G28">
-        <v>354</v>
+        <v>171.4285714285684</v>
       </c>
       <c r="H28">
-        <v>0.8012402294181287</v>
+        <v>0.8012403290385091</v>
       </c>
       <c r="I28">
-        <v>0.7024965151331453</v>
+        <v>0.7027607436612853</v>
       </c>
     </row>
     <row r="29">
@@ -1422,19 +1422,19 @@
         </is>
       </c>
       <c r="E29">
-        <v>-0.3723656444047009</v>
+        <v>-0.3723656444047052</v>
       </c>
       <c r="F29">
-        <v>0.3828672795078218</v>
+        <v>0.3828672319048934</v>
       </c>
       <c r="G29">
-        <v>354</v>
+        <v>171.4285714285705</v>
       </c>
       <c r="H29">
-        <v>-0.972571082290916</v>
+        <v>-0.9725712032133456</v>
       </c>
       <c r="I29">
-        <v>0.5946975014654112</v>
+        <v>0.59518105167782</v>
       </c>
     </row>
     <row r="30">
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="E30">
-        <v>-0.4931016035313918</v>
+        <v>-0.4931016035313958</v>
       </c>
       <c r="F30">
-        <v>0.3828672795078226</v>
+        <v>0.3828672319048945</v>
       </c>
       <c r="G30">
-        <v>354</v>
+        <v>171.4285714285705</v>
       </c>
       <c r="H30">
-        <v>-1.287917850188911</v>
+        <v>-1.287918010319264</v>
       </c>
       <c r="I30">
-        <v>0.4029154339065094</v>
+        <v>0.4039133828672478</v>
       </c>
     </row>
     <row r="31">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="E31">
-        <v>-0.1207359591266909</v>
+        <v>-0.1207359591266906</v>
       </c>
       <c r="F31">
-        <v>0.3828672795078222</v>
+        <v>0.3828672319048955</v>
       </c>
       <c r="G31">
-        <v>354</v>
+        <v>171.4285714285705</v>
       </c>
       <c r="H31">
-        <v>-0.3153467678979975</v>
+        <v>-0.3153468071059199</v>
       </c>
       <c r="I31">
-        <v>0.9466687211981195</v>
+        <v>0.9466773219194933</v>
       </c>
     </row>
   </sheetData>
